--- a/QA/Test-Cases.xlsx
+++ b/QA/Test-Cases.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pro\source\repos\SauceDemo-Manual-Testing\QA\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA73A63F-2256-4147-939F-B3D815CBCA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,13 +20,339 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="106">
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Test Scenario</t>
+  </si>
+  <si>
+    <t>Preconditions</t>
+  </si>
+  <si>
+    <t>Test Data</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Test Type</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Defect ID</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>Login with valid credentials</t>
+  </si>
+  <si>
+    <t>Login with invalid password</t>
+  </si>
+  <si>
+    <t>Login with empty fields</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>User is on login page</t>
+  </si>
+  <si>
+    <t>Valid credentials</t>
+  </si>
+  <si>
+    <t>Wrong password</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        </t>
+  </si>
+  <si>
+    <t>Functional / Positive</t>
+  </si>
+  <si>
+    <t>Functional / Negative</t>
+  </si>
+  <si>
+    <t>Products page displayed</t>
+  </si>
+  <si>
+    <t>Error message displayed</t>
+  </si>
+  <si>
+    <t>TC-LOG-001</t>
+  </si>
+  <si>
+    <t>TC-LOG-002</t>
+  </si>
+  <si>
+    <t>TC-LOG-003</t>
+  </si>
+  <si>
+    <t>TC-PROD-004</t>
+  </si>
+  <si>
+    <t>TC-PROD-005</t>
+  </si>
+  <si>
+    <t>TC-PROD-006</t>
+  </si>
+  <si>
+    <t>TC-PROD-007</t>
+  </si>
+  <si>
+    <t>TC-PROD-016</t>
+  </si>
+  <si>
+    <t>TC-PROD-017</t>
+  </si>
+  <si>
+    <t>Produits</t>
+  </si>
+  <si>
+    <t>Cart</t>
+  </si>
+  <si>
+    <t>TC-Cart-008</t>
+  </si>
+  <si>
+    <t>TC-Cart-009</t>
+  </si>
+  <si>
+    <t>TC-Cart-010</t>
+  </si>
+  <si>
+    <t>verify buttons and description</t>
+  </si>
+  <si>
+    <t>verify images</t>
+  </si>
+  <si>
+    <t>verify button cart</t>
+  </si>
+  <si>
+    <t>Log out</t>
+  </si>
+  <si>
+    <t>verify log out</t>
+  </si>
+  <si>
+    <t>User is login</t>
+  </si>
+  <si>
+    <t>Functional/Positive</t>
+  </si>
+  <si>
+    <t>User is login,he is products page</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>button to increase  quantity of product</t>
+  </si>
+  <si>
+    <t>user able to increase quantity</t>
+  </si>
+  <si>
+    <t>user can't increase quantity</t>
+  </si>
+  <si>
+    <t>TC-CEKout-014</t>
+  </si>
+  <si>
+    <t>Checkout</t>
+  </si>
+  <si>
+    <t>empty fields</t>
+  </si>
+  <si>
+    <t>empty firstname</t>
+  </si>
+  <si>
+    <t>empty lastname</t>
+  </si>
+  <si>
+    <t>empty code postal</t>
+  </si>
+  <si>
+    <t>remove product</t>
+  </si>
+  <si>
+    <t>add product</t>
+  </si>
+  <si>
+    <t>Product sorting</t>
+  </si>
+  <si>
+    <t>TC-PROD-020</t>
+  </si>
+  <si>
+    <t>firstname &amp; lastname</t>
+  </si>
+  <si>
+    <t>firstname &amp; code postal</t>
+  </si>
+  <si>
+    <t>lastname &amp; code postal</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>button cart not in correct place</t>
+  </si>
+  <si>
+    <t>User is login with username=visual_user</t>
+  </si>
+  <si>
+    <t>button checkout in incorrect place</t>
+  </si>
+  <si>
+    <t>Functional/Negative</t>
+  </si>
+  <si>
+    <t>User is login with username=error_user</t>
+  </si>
+  <si>
+    <t>button finish don't work</t>
+  </si>
+  <si>
+    <t>speed of sorting products</t>
+  </si>
+  <si>
+    <t>login username=performance_glitch_user</t>
+  </si>
+  <si>
+    <t>should be in the right top</t>
+  </si>
+  <si>
+    <t>it's in the centre</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>BUG-001</t>
+  </si>
+  <si>
+    <t>BUG-002</t>
+  </si>
+  <si>
+    <t>BUG-003</t>
+  </si>
+  <si>
+    <t>BUG-004</t>
+  </si>
+  <si>
+    <t>should be in the bottom</t>
+  </si>
+  <si>
+    <t>it's in the top</t>
+  </si>
+  <si>
+    <t>TC-CEKout-011</t>
+  </si>
+  <si>
+    <t>TC-CEKout-012</t>
+  </si>
+  <si>
+    <t>TC-CEKout-013</t>
+  </si>
+  <si>
+    <t>TC-LOUT-015</t>
+  </si>
+  <si>
+    <t>TC-CEKout-018</t>
+  </si>
+  <si>
+    <t>TC-CEKout-019</t>
+  </si>
+  <si>
+    <t>show an error</t>
+  </si>
+  <si>
+    <t>user log out and go to the login page</t>
+  </si>
+  <si>
+    <t>BUG-005</t>
+  </si>
+  <si>
+    <t>added successfully</t>
+  </si>
+  <si>
+    <t>exists and works</t>
+  </si>
+  <si>
+    <t>every product has the right image</t>
+  </si>
+  <si>
+    <t>all products have image of animal</t>
+  </si>
+  <si>
+    <t>remove successfully</t>
+  </si>
+  <si>
+    <t>sotoring in right way</t>
+  </si>
+  <si>
+    <t xml:space="preserve">user finish checkout and print </t>
+  </si>
+  <si>
+    <t>finish don't work and user can't move on</t>
+  </si>
+  <si>
+    <t xml:space="preserve">products storing quickly </t>
+  </si>
+  <si>
+    <t>the fonction take time to happen</t>
+  </si>
+  <si>
+    <t>user can see buttons and description</t>
+  </si>
+  <si>
+    <t>images are ligible and mutch to product</t>
+  </si>
+  <si>
+    <t>BUG-006</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,13 +360,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,8 +405,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +689,709 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.08984375" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" customWidth="1"/>
+    <col min="3" max="3" width="34.6328125" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="37" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="19.26953125" customWidth="1"/>
+    <col min="8" max="8" width="34.1796875" customWidth="1"/>
+    <col min="9" max="9" width="35.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" t="s">
+        <v>103</v>
+      </c>
+      <c r="I5" t="s">
+        <v>103</v>
+      </c>
+      <c r="J5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I6" t="s">
+        <v>104</v>
+      </c>
+      <c r="J6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" t="s">
+        <v>93</v>
+      </c>
+      <c r="I8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" t="s">
+        <v>94</v>
+      </c>
+      <c r="I9" t="s">
+        <v>94</v>
+      </c>
+      <c r="J9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" t="s">
+        <v>90</v>
+      </c>
+      <c r="I12" t="s">
+        <v>90</v>
+      </c>
+      <c r="J12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" t="s">
+        <v>90</v>
+      </c>
+      <c r="I13" t="s">
+        <v>90</v>
+      </c>
+      <c r="J13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" t="s">
+        <v>90</v>
+      </c>
+      <c r="I14" t="s">
+        <v>90</v>
+      </c>
+      <c r="J14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" t="s">
+        <v>90</v>
+      </c>
+      <c r="I15" t="s">
+        <v>90</v>
+      </c>
+      <c r="J15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I16" t="s">
+        <v>91</v>
+      </c>
+      <c r="J16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" t="s">
+        <v>97</v>
+      </c>
+      <c r="I17" t="s">
+        <v>97</v>
+      </c>
+      <c r="J17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" t="s">
+        <v>98</v>
+      </c>
+      <c r="I18" t="s">
+        <v>98</v>
+      </c>
+      <c r="J18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/QA/Test-Cases.xlsx
+++ b/QA/Test-Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pro\source\repos\SauceDemo-Manual-Testing\QA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA73A63F-2256-4147-939F-B3D815CBCA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA9A8E8-7786-48EB-92CD-8E4ECC3D10AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="107">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -180,9 +180,6 @@
     <t>button to increase  quantity of product</t>
   </si>
   <si>
-    <t>user able to increase quantity</t>
-  </si>
-  <si>
     <t>user can't increase quantity</t>
   </si>
   <si>
@@ -327,9 +324,6 @@
     <t>sotoring in right way</t>
   </si>
   <si>
-    <t xml:space="preserve">user finish checkout and print </t>
-  </si>
-  <si>
     <t>finish don't work and user can't move on</t>
   </si>
   <si>
@@ -346,6 +340,15 @@
   </si>
   <si>
     <t>BUG-006</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>user can  increase quantity</t>
+  </si>
+  <si>
+    <t>user finish checkout and print invoice</t>
   </si>
 </sst>
 </file>
@@ -771,7 +774,7 @@
         <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -803,7 +806,7 @@
         <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
@@ -835,7 +838,7 @@
         <v>24</v>
       </c>
       <c r="J4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
@@ -859,13 +862,13 @@
         <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
@@ -889,13 +892,13 @@
         <v>21</v>
       </c>
       <c r="H6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
@@ -912,26 +915,26 @@
         <v>47</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
@@ -942,7 +945,7 @@
         <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
@@ -955,13 +958,13 @@
         <v>21</v>
       </c>
       <c r="H8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
@@ -985,13 +988,13 @@
         <v>21</v>
       </c>
       <c r="H9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
@@ -1015,19 +1018,19 @@
         <v>48</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
@@ -1038,43 +1041,43 @@
         <v>35</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>47</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="K11" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s">
         <v>53</v>
-      </c>
-      <c r="C12" t="s">
-        <v>54</v>
       </c>
       <c r="D12" t="s">
         <v>16</v>
@@ -1087,24 +1090,24 @@
         <v>22</v>
       </c>
       <c r="H12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
@@ -1113,30 +1116,30 @@
         <v>44</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G13" t="s">
         <v>22</v>
       </c>
       <c r="H13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
         <v>16</v>
@@ -1145,30 +1148,30 @@
         <v>44</v>
       </c>
       <c r="F14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G14" t="s">
         <v>22</v>
       </c>
       <c r="H14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" t="s">
         <v>52</v>
       </c>
-      <c r="B15" t="s">
-        <v>53</v>
-      </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
         <v>16</v>
@@ -1177,24 +1180,24 @@
         <v>44</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G15" t="s">
         <v>22</v>
       </c>
       <c r="H15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
         <v>42</v>
@@ -1213,13 +1216,13 @@
         <v>45</v>
       </c>
       <c r="H16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
@@ -1230,7 +1233,7 @@
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
         <v>16</v>
@@ -1243,13 +1246,13 @@
         <v>45</v>
       </c>
       <c r="H17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
@@ -1260,7 +1263,7 @@
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
         <v>16</v>
@@ -1273,121 +1276,121 @@
         <v>45</v>
       </c>
       <c r="H18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>47</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="3" t="s">
         <v>48</v>
       </c>
       <c r="H19" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>47</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>47</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="3" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
